--- a/main/04_data_extraction/individual_reading.xlsx
+++ b/main/04_data_extraction/individual_reading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\orincon\scoping-ml-wave-seismology\main\04_data_extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBA3D48-EAB4-4754-BC97-D94457E4381B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D954BE61-5C76-48C0-9249-DF48066B7845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{115BB8D9-8B86-4726-97F8-E06477FD353D}"/>
   </bookViews>
@@ -370,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="437">
   <si>
     <t>Lectura general</t>
   </si>
@@ -1183,9 +1183,6 @@
 3.  Automatic differentiation in PyTorch provides an efficient and reliable way to compute gradients, eliminating the need for manual adjoint testing.
 4.Using automatic differentiation to calculate gradients in seismic inversion, avoiding the need for adjoint tests. 
 5. The article is well written and clearly explains the network architecture and investment process.</t>
-  </si>
-  <si>
-    <t>SWINet</t>
   </si>
   <si>
     <t>It allows gradients to be calculated more easily than with traditional seismic inversion methods.</t>
@@ -1815,12 +1812,125 @@
   <si>
     <t>Misfit function based on L2 waveform difference and Comparison with conventional elastic FWI.</t>
   </si>
+  <si>
+    <t>1D</t>
+  </si>
+  <si>
+    <t>SWINet. A sequence of forward-modeling cells implementing the discrete acoustic wave equation.</t>
+  </si>
+  <si>
+    <t>  finite-difference</t>
+  </si>
+  <si>
+    <t>In-house solver </t>
+  </si>
+  <si>
+    <t>  Synthetic data</t>
+  </si>
+  <si>
+    <t>Larger 2D/3D models remain challenging and may require CPU memory or multi-GPU strategies. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The method is built around the discrete update rule of the acoustic equation. The Laplacian is implemented via convolution (efficient on GPUs).</t>
+  </si>
+  <si>
+    <t>  The method is essentially FWI reformulated as a neural network optimization problem.</t>
+  </si>
+  <si>
+    <t>22. Fang et al. (2024)</t>
+  </si>
+  <si>
+    <t> 1)  Analysis of an existing method.
+2) Rock physics modeling for VsV_sVs prediction
+3) The physics is relevant to elastic wave behavior in porous media.
+4) Proposes a DNN-based workflow constrained by poroelasticity theory to predict shear-wave velocity Vs
+5) The paper is generally well structured, with a clear separation between the DNN-based method, the rock physics modeling workflow, and the comparative evaluation.</t>
+  </si>
+  <si>
+    <t> A fully-connected NN</t>
+  </si>
+  <si>
+    <t> Can work with few Vs labels</t>
+  </si>
+  <si>
+    <t>  PyTorch</t>
+  </si>
+  <si>
+    <t>  Not applicable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Not the case.</t>
+  </si>
+  <si>
+    <t> Real data. Well-log datasets from 16 wells for training.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1D (depth-dependent well logs). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Not discussed. </t>
+  </si>
+  <si>
+    <t>Poroelastic. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The model uses poroelastic relations to reduce dependence on Vs labels. </t>
+  </si>
+  <si>
+    <t> DNN requires sufficient training data for best performance and comparative analysis with other network designs.</t>
+  </si>
+  <si>
+    <t>Comparison of predicted curves vs well-log curves.</t>
+  </si>
+  <si>
+    <t>It solves a parameter prediction problem. Estimate Vs from logs and poroelastic relations.</t>
+  </si>
+  <si>
+    <t>Physics-guided regression with a NN.</t>
+  </si>
+  <si>
+    <t> 1) Research prototype
+2) ML for seismic monitoring and time-lapse interpretation
+3) Leak can be represented by a region in the subsurface. Main concern is the synthetic-to-real gap
+4) A supervised ML method for underground hydrogen storage leakage detection
+5) The workflow is understandable</t>
+  </si>
+  <si>
+    <t> Works with very sparse data.</t>
+  </si>
+  <si>
+    <t>  In-house solver</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Synthetic </t>
+  </si>
+  <si>
+    <t> Elastic</t>
+  </si>
+  <si>
+    <t> More appropriate to describe the complex time-lapse changes caused by CO2 leakage.</t>
+  </si>
+  <si>
+    <t> Physics-based synthetic data to train a supervised regression</t>
+  </si>
+  <si>
+    <t> Estimating leak bounding box, mass and volume from time-lapse waveforms.</t>
+  </si>
+  <si>
+    <t>Likely extension to more realistic scenarios with noise robustness.</t>
+  </si>
+  <si>
+    <t>Error distributions (misfit histograms / Gaussian fits) and visual overlap of predicted vs true leakage regions</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HydrogenNet (hybrid 2D CNN with fully-connected DNN).</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1855,11 +1965,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
@@ -1871,30 +1976,18 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE97132"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1943,8 +2036,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1957,7 +2054,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2008,76 +2105,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2087,12 +2114,61 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2545,39 +2621,39 @@
   <sheetData>
     <row r="1" spans="1:16" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43" t="s">
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="43"/>
+      <c r="G1" s="19"/>
       <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="I1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43" t="s">
+      <c r="J1" s="19"/>
+      <c r="K1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="43"/>
-      <c r="M1" s="44" t="s">
+      <c r="L1" s="19"/>
+      <c r="M1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="44" t="s">
+      <c r="N1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="44" t="s">
+      <c r="O1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="42" t="s">
+      <c r="P1" s="18" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2585,7 +2661,7 @@
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="44"/>
+      <c r="B2" s="20"/>
       <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
@@ -2616,10 +2692,10 @@
       <c r="L2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="42"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="18"/>
     </row>
     <row r="3" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
@@ -5629,2156 +5705,2162 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C33CE99-2E5D-4F6C-B637-1B3AEFE552A0}">
   <dimension ref="A1:Q46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.09765625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.09765625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.59765625" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.296875" style="21" customWidth="1"/>
-    <col min="3" max="3" width="36.59765625" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.8984375" style="21" customWidth="1"/>
-    <col min="5" max="8" width="36.59765625" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.69921875" style="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="36.59765625" style="21" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="32.296875" style="21" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.09765625" style="21"/>
+    <col min="1" max="1" width="36.59765625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.296875" style="25" customWidth="1"/>
+    <col min="3" max="3" width="36.59765625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.8984375" style="25" customWidth="1"/>
+    <col min="5" max="8" width="36.59765625" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="36.59765625" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.296875" style="25" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.09765625" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18"/>
-      <c r="B1" s="45" t="s">
+      <c r="A1" s="21"/>
+      <c r="B1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42" t="s">
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="20" t="s">
+      <c r="G1" s="23"/>
+      <c r="H1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="42" t="s">
+      <c r="I1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42" t="s">
+      <c r="J1" s="23"/>
+      <c r="K1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="45" t="s">
+      <c r="L1" s="23"/>
+      <c r="M1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="45" t="s">
+      <c r="N1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="45" t="s">
+      <c r="O1" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="19" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
     </row>
     <row r="3" spans="1:15" ht="345" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="240" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="K4" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="M4" s="27"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="270" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="K5" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="L5" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="O5" s="21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="255" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="L6" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M6" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="N6" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O6" s="21" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="330" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="N7" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O7" s="21" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="375" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="M8" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="N8" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O8" s="21" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="270" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="N9" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O9" s="21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="I10" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="J10" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="N10" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O10" s="21" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="270" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="L11" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="N11" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O11" s="21" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="255" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="I12" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="K12" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="L12" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M12" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="N12" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O12" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="390" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="K13" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="L13" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="N13" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="O13" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="I14" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="K14" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="L14" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M14" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N14" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O14" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="255" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="27">
         <v>2</v>
       </c>
-      <c r="J3" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="K3" s="22" t="s">
+      <c r="J15" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="M15" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N15" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="21" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="31" customFormat="1" ht="405" x14ac:dyDescent="0.25">
+      <c r="A16" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>403</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>404</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>405</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>406</v>
+      </c>
+      <c r="I16" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="J16" s="30" t="s">
+        <v>407</v>
+      </c>
+      <c r="K16" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="L16" s="30" t="s">
+        <v>408</v>
+      </c>
+      <c r="M16" s="30" t="s">
+        <v>409</v>
+      </c>
+      <c r="N16" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="O16" s="29" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="31" customFormat="1" ht="180" x14ac:dyDescent="0.25">
+      <c r="A17" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>374</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>363</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="I17" s="30" t="s">
+        <v>368</v>
+      </c>
+      <c r="J17" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="K17" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="L17" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="M17" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="N17" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="O17" s="30" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="379.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="I18" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="N18" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="O18" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="31" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="I19" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="J19" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="K19" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="L19" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="M19" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="N19" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="O19" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="P19" s="33" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="K20" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L20" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="M3" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="N3" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="O3" s="22" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="240" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" s="24" t="s">
+      <c r="M20" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="N20" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O20" s="35" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="31" customFormat="1" ht="165" x14ac:dyDescent="0.25">
+      <c r="A21" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>376</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>377</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>379</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="H21" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="I21" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>382</v>
+      </c>
+      <c r="K21" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="L21" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="M21" s="30" t="s">
+        <v>385</v>
+      </c>
+      <c r="N21" s="30" t="s">
+        <v>388</v>
+      </c>
+      <c r="O21" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="P21" s="31" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" s="31" customFormat="1" ht="210" x14ac:dyDescent="0.25">
+      <c r="A22" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>392</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>394</v>
+      </c>
+      <c r="G22" s="30" t="s">
+        <v>393</v>
+      </c>
+      <c r="H22" s="30" t="s">
+        <v>395</v>
+      </c>
+      <c r="I22" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="J22" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="K22" s="29" t="s">
+        <v>396</v>
+      </c>
+      <c r="L22" s="30" t="s">
+        <v>397</v>
+      </c>
+      <c r="M22" s="30" t="s">
+        <v>398</v>
+      </c>
+      <c r="N22" s="30" t="s">
+        <v>399</v>
+      </c>
+      <c r="O22" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="P22" s="31" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="315" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>272</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="I23" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="K23" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="L23" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M23" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="N23" s="21"/>
+      <c r="O23" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="P23" s="21" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" s="31" customFormat="1" ht="180" x14ac:dyDescent="0.25">
+      <c r="A24" s="29" t="s">
+        <v>410</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>411</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>414</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>416</v>
+      </c>
+      <c r="G24" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="H24" s="30" t="s">
+        <v>417</v>
+      </c>
+      <c r="I24" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="J24" s="30" t="s">
+        <v>419</v>
+      </c>
+      <c r="K24" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="L24" s="30" t="s">
+        <v>421</v>
+      </c>
+      <c r="M24" s="30" t="s">
+        <v>425</v>
+      </c>
+      <c r="N24" s="30" t="s">
+        <v>424</v>
+      </c>
+      <c r="O24" s="29" t="s">
+        <v>422</v>
+      </c>
+      <c r="P24" s="33" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="31" customFormat="1" ht="150" x14ac:dyDescent="0.25">
+      <c r="A25" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>426</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>427</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>404</v>
+      </c>
+      <c r="G25" s="30" t="s">
+        <v>428</v>
+      </c>
+      <c r="H25" s="30" t="s">
+        <v>429</v>
+      </c>
+      <c r="I25" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="J25" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="K25" s="30" t="s">
+        <v>430</v>
+      </c>
+      <c r="L25" s="29" t="s">
+        <v>431</v>
+      </c>
+      <c r="M25" s="29" t="s">
+        <v>432</v>
+      </c>
+      <c r="N25" s="29" t="s">
+        <v>433</v>
+      </c>
+      <c r="O25" s="29" t="s">
+        <v>434</v>
+      </c>
+      <c r="P25" s="33" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="330" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="F26" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G26" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="H26" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="I26" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="J26" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="H4" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="I4" s="24">
-        <v>2</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="M4" s="24"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="270" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="G5" s="26" t="s">
+      <c r="K26" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="L26" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="H5" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="I5" s="26">
-        <v>2</v>
-      </c>
-      <c r="J5" s="26" t="s">
+      <c r="M26" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O27" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="300" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="I28" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="J28" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="K28" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="L28" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="M28" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="N28" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="O28" s="21" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="31" customFormat="1" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A29" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>302</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="F29" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="G29" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="H29" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="I29" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="J29" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="K29" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="L29" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="M29" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="N29" s="29" t="s">
+        <v>313</v>
+      </c>
+      <c r="O29" s="29" t="s">
+        <v>314</v>
+      </c>
+      <c r="P29" s="33" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" s="31" customFormat="1" ht="315" x14ac:dyDescent="0.25">
+      <c r="A30" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>336</v>
+      </c>
+      <c r="F30" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="G30" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="H30" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="I30" s="30" t="s">
+        <v>339</v>
+      </c>
+      <c r="J30" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="K30" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="L30" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="M30" s="37" t="s">
+        <v>343</v>
+      </c>
+      <c r="N30" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="O30" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="P30" s="33" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" s="31" customFormat="1" ht="180" x14ac:dyDescent="0.25">
+      <c r="A31" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>350</v>
+      </c>
+      <c r="E31" s="38" t="s">
+        <v>361</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="G31" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="H31" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="I31" s="30" t="s">
+        <v>354</v>
+      </c>
+      <c r="J31" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="K31" s="30" t="s">
+        <v>355</v>
+      </c>
+      <c r="L31" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="M31" s="30" t="s">
+        <v>357</v>
+      </c>
+      <c r="N31" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="O31" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="P31" s="30" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q31" s="39"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M32" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N32" s="21"/>
+      <c r="O32" s="27" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="390" x14ac:dyDescent="0.25">
+      <c r="A33" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="E33" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="K5" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="N5" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="O5" s="25" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="255" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="I6" s="26">
-        <v>2</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="K6" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="L6" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="N6" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O6" s="25" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="330" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="I7" s="26">
-        <v>3</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="K7" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="L7" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="M7" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="N7" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="375" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I8" s="26">
-        <v>3</v>
-      </c>
-      <c r="J8" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="K8" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="M8" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="N8" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O8" s="25" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="270" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="I9" s="26">
-        <v>1</v>
-      </c>
-      <c r="J9" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="L9" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="M9" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="N9" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O9" s="25" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="409.6" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="H10" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="I10" s="26">
-        <v>1</v>
-      </c>
-      <c r="J10" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="L10" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="M10" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="N10" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O10" s="25" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="270" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="I11" s="26">
-        <v>2</v>
-      </c>
-      <c r="J11" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="K11" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="L11" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="M11" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="N11" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O11" s="25" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="255" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="I12" s="26">
-        <v>3</v>
-      </c>
-      <c r="J12" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="K12" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="L12" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="M12" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="N12" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O12" s="25" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="390" x14ac:dyDescent="0.25">
-      <c r="A13" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="I13" s="26">
-        <v>2</v>
-      </c>
-      <c r="J13" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="K13" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="L13" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="M13" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="N13" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="O13" s="25" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="409.6" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="I14" s="26">
-        <v>1</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="K14" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="L14" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="M14" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N14" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O14" s="25" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="255" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H15" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I15" s="26">
-        <v>2</v>
-      </c>
-      <c r="J15" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K15" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="L15" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="M15" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N15" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O15" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="405" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H16" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I16" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="J16" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K16" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="L16" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="M16" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N16" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="O16" s="25" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" s="34" customFormat="1" ht="180" x14ac:dyDescent="0.25">
-      <c r="A17" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="40" t="s">
-        <v>375</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>364</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>365</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>366</v>
-      </c>
-      <c r="G17" s="41" t="s">
-        <v>367</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>368</v>
-      </c>
-      <c r="I17" s="33" t="s">
-        <v>369</v>
-      </c>
-      <c r="J17" s="33" t="s">
-        <v>370</v>
-      </c>
-      <c r="K17" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="L17" s="33" t="s">
-        <v>371</v>
-      </c>
-      <c r="M17" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="N17" s="33" t="s">
-        <v>374</v>
-      </c>
-      <c r="O17" s="33" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="379.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>246</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>248</v>
-      </c>
-      <c r="I18" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="J18" s="25" t="s">
-        <v>250</v>
-      </c>
-      <c r="K18" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="L18" s="25" t="s">
-        <v>252</v>
-      </c>
-      <c r="M18" s="25" t="s">
-        <v>253</v>
-      </c>
-      <c r="N18" s="25" t="s">
-        <v>254</v>
-      </c>
-      <c r="O18" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" s="34" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>255</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>256</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>258</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="G19" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="H19" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="I19" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="J19" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="L19" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="M19" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="N19" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="O19" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="P19" s="35" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="409.6" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>270</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="G20" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="H20" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="I20" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="J20" s="25" t="s">
-        <v>271</v>
-      </c>
-      <c r="K20" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="L20" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="M20" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="N20" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O20" s="30" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" s="34" customFormat="1" ht="165" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>376</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>377</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>378</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>379</v>
-      </c>
-      <c r="F21" s="33" t="s">
-        <v>380</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>339</v>
-      </c>
-      <c r="H21" s="33" t="s">
-        <v>381</v>
-      </c>
-      <c r="I21" s="33" t="s">
-        <v>382</v>
-      </c>
-      <c r="J21" s="33" t="s">
-        <v>383</v>
-      </c>
-      <c r="K21" s="33" t="s">
-        <v>385</v>
-      </c>
-      <c r="L21" s="33" t="s">
-        <v>384</v>
-      </c>
-      <c r="M21" s="33" t="s">
-        <v>386</v>
-      </c>
-      <c r="N21" s="33" t="s">
-        <v>389</v>
-      </c>
-      <c r="O21" s="33" t="s">
-        <v>387</v>
-      </c>
-      <c r="P21" s="34" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" s="34" customFormat="1" ht="210" x14ac:dyDescent="0.25">
-      <c r="A22" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="32" t="s">
-        <v>390</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>391</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>393</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>392</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>395</v>
-      </c>
-      <c r="G22" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="H22" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="I22" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="J22" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="K22" s="46" t="s">
-        <v>397</v>
-      </c>
-      <c r="L22" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="M22" s="33" t="s">
-        <v>399</v>
-      </c>
-      <c r="N22" s="33" t="s">
-        <v>400</v>
-      </c>
-      <c r="O22" s="33" t="s">
-        <v>401</v>
-      </c>
-      <c r="P22" s="34" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" ht="315" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>274</v>
-      </c>
-      <c r="D23" s="25" t="s">
+      <c r="F33" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="G33" s="27" t="s">
         <v>275</v>
       </c>
-      <c r="E23" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>277</v>
-      </c>
-      <c r="I23" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="J23" s="25" t="s">
-        <v>278</v>
-      </c>
-      <c r="K23" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="L23" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M23" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25" t="s">
-        <v>280</v>
-      </c>
-      <c r="P23" s="25" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N24" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O24" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N25" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O25" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" ht="330" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>282</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>284</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="G26" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="H26" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="I26" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="J26" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="L26" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="M26" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N26" s="25"/>
-      <c r="O26" s="25" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O27" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="300" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>288</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>290</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G28" s="26" t="s">
-        <v>293</v>
-      </c>
-      <c r="H28" s="25" t="s">
-        <v>294</v>
-      </c>
-      <c r="I28" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="J28" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="K28" s="25" t="s">
-        <v>297</v>
-      </c>
-      <c r="L28" s="25" t="s">
-        <v>298</v>
-      </c>
-      <c r="M28" s="25" t="s">
-        <v>299</v>
-      </c>
-      <c r="N28" s="25" t="s">
-        <v>300</v>
-      </c>
-      <c r="O28" s="25" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" s="34" customFormat="1" ht="409.6" x14ac:dyDescent="0.25">
-      <c r="A29" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>302</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>303</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>305</v>
-      </c>
-      <c r="F29" s="32" t="s">
-        <v>306</v>
-      </c>
-      <c r="G29" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="H29" s="32" t="s">
-        <v>308</v>
-      </c>
-      <c r="I29" s="32" t="s">
-        <v>309</v>
-      </c>
-      <c r="J29" s="32" t="s">
-        <v>310</v>
-      </c>
-      <c r="K29" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="L29" s="32" t="s">
-        <v>312</v>
-      </c>
-      <c r="M29" s="32" t="s">
-        <v>313</v>
-      </c>
-      <c r="N29" s="32" t="s">
-        <v>314</v>
-      </c>
-      <c r="O29" s="32" t="s">
-        <v>315</v>
-      </c>
-      <c r="P29" s="36" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" s="34" customFormat="1" ht="315" x14ac:dyDescent="0.25">
-      <c r="A30" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>334</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>335</v>
-      </c>
-      <c r="D30" s="33" t="s">
-        <v>336</v>
-      </c>
-      <c r="E30" s="33" t="s">
-        <v>337</v>
-      </c>
-      <c r="F30" s="33" t="s">
-        <v>338</v>
-      </c>
-      <c r="G30" s="33" t="s">
-        <v>339</v>
-      </c>
-      <c r="H30" s="33" t="s">
-        <v>348</v>
-      </c>
-      <c r="I30" s="33" t="s">
-        <v>340</v>
-      </c>
-      <c r="J30" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="K30" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="L30" s="33" t="s">
-        <v>343</v>
-      </c>
-      <c r="M30" s="37" t="s">
-        <v>344</v>
-      </c>
-      <c r="N30" s="32" t="s">
-        <v>345</v>
-      </c>
-      <c r="O30" s="33" t="s">
-        <v>347</v>
-      </c>
-      <c r="P30" s="35" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" s="34" customFormat="1" ht="180" x14ac:dyDescent="0.3">
-      <c r="A31" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="C31" s="33" t="s">
-        <v>350</v>
-      </c>
-      <c r="D31" s="33" t="s">
-        <v>351</v>
-      </c>
-      <c r="E31" s="38" t="s">
-        <v>362</v>
-      </c>
-      <c r="F31" s="33" t="s">
-        <v>352</v>
-      </c>
-      <c r="G31" s="33" t="s">
-        <v>353</v>
-      </c>
-      <c r="H31" s="33" t="s">
-        <v>354</v>
-      </c>
-      <c r="I31" s="33" t="s">
-        <v>355</v>
-      </c>
-      <c r="J31" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="K31" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="L31" s="33" t="s">
-        <v>357</v>
-      </c>
-      <c r="M31" s="33" t="s">
-        <v>358</v>
-      </c>
-      <c r="N31" s="32" t="s">
-        <v>359</v>
-      </c>
-      <c r="O31" s="33" t="s">
-        <v>361</v>
-      </c>
-      <c r="P31" s="33" t="s">
-        <v>360</v>
-      </c>
-      <c r="Q31" s="39"/>
-    </row>
-    <row r="32" spans="1:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N32" s="25"/>
-      <c r="O32" s="26" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="390" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="25" t="s">
-        <v>318</v>
-      </c>
-      <c r="C33" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>320</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="F33" s="26" t="s">
+      <c r="H33" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="G33" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="H33" s="25" t="s">
+      <c r="I33" s="27" t="s">
         <v>322</v>
       </c>
-      <c r="I33" s="26" t="s">
+      <c r="J33" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="J33" s="25" t="s">
+      <c r="K33" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="K33" s="26" t="s">
+      <c r="L33" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="M33" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="L33" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="M33" s="25" t="s">
+      <c r="N33" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="N33" s="25" t="s">
+      <c r="O33" s="27"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H34" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I34" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J34" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K34" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L34" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M34" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N34" s="21"/>
+      <c r="O34" s="27" t="s">
         <v>327</v>
       </c>
-      <c r="O33" s="26"/>
-    </row>
-    <row r="34" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M34" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N34" s="25"/>
-      <c r="O34" s="26" t="s">
+    </row>
+    <row r="35" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A35" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N35" s="21" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" ht="75" x14ac:dyDescent="0.25">
-      <c r="A35" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G35" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H35" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I35" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J35" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K35" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L35" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M35" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N35" s="25" t="s">
+      <c r="O35" s="27"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F36" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H36" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I36" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J36" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K36" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L36" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M36" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N36" s="21"/>
+      <c r="O36" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="O35" s="26"/>
-    </row>
-    <row r="36" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A36" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F36" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G36" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H36" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I36" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J36" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K36" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L36" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M36" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N36" s="25"/>
-      <c r="O36" s="26" t="s">
+    </row>
+    <row r="37" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M37" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N37" s="21" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N37" s="25" t="s">
+      <c r="O37" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M38" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N38" s="21"/>
+      <c r="O38" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="90" x14ac:dyDescent="0.25">
+      <c r="A39" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M39" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N39" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="O37" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A38" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F38" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G38" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H38" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I38" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J38" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K38" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L38" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M38" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N38" s="25"/>
-      <c r="O38" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="90" x14ac:dyDescent="0.25">
-      <c r="A39" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M39" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N39" s="25" t="s">
+      <c r="O39" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N40" s="21"/>
+      <c r="O40" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+      <c r="A41" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N41" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="O39" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A40" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F40" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G40" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H40" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I40" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J40" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K40" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L40" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M40" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N40" s="25"/>
-      <c r="O40" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="105" x14ac:dyDescent="0.25">
-      <c r="A41" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D41" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F41" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G41" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H41" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I41" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J41" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K41" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L41" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M41" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N41" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="O41" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A42" s="25" t="s">
+      <c r="O41" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N42" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O42" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A43" s="25" t="s">
+      <c r="B42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O42" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N43" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O43" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A44" s="25" t="s">
+      <c r="B43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N43" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O43" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N44" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O44" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A45" s="25" t="s">
+      <c r="B44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N44" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O44" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B45" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D45" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E45" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F45" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G45" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H45" s="25"/>
-      <c r="I45" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="J45" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K45" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L45" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M45" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N45" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="O45" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A46" s="28" t="s">
+      <c r="B45" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F45" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G45" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H45" s="21"/>
+      <c r="I45" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J45" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K45" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L45" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M45" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N45" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O45" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="F46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="G46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="H46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="I46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="J46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="K46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="L46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="M46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="N46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="O46" s="29" t="s">
+      <c r="B46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="J46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="M46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N46" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O46" s="27" t="s">
         <v>88</v>
       </c>
     </row>
@@ -7799,6 +7881,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010009048CEEA230F14796749F6DFD5F5263" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5105af4e7c1b0ed6cdb04338eaf51f7a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="96457c7a-bdfc-427e-9d05-5faa5ab5244b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0baee1a300280ca08e7397f1756276d6" ns2:_="">
     <xsd:import namespace="96457c7a-bdfc-427e-9d05-5faa5ab5244b"/>
@@ -7942,22 +8039,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1160EB8C-E200-4916-A3B3-9BF8115D37F8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F2579D-323E-48EA-8FED-D372AFFF0A04}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75ADFBF6-8C74-4292-833E-68A026E87063}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7973,21 +8072,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F2579D-323E-48EA-8FED-D372AFFF0A04}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1160EB8C-E200-4916-A3B3-9BF8115D37F8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>